--- a/analise_eua/energia_eletrica/vistra/vst_10q.xlsx
+++ b/analise_eua/energia_eletrica/vistra/vst_10q.xlsx
@@ -433,56 +433,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -493,51 +496,54 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>435</v>
+      </c>
+      <c r="C2" t="n">
         <v>634</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>602</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>458</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>561</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>905</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1624</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1070</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3170</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>643</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>518</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>535</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1871</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1022</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>351</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>444</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>561</v>
       </c>
     </row>
@@ -548,51 +554,54 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>41</v>
+      </c>
+      <c r="C3" t="n">
         <v>37</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>30</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>31</v>
-      </c>
-      <c r="E3" t="n">
-        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
       </c>
       <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="n">
         <v>23</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>32</v>
-      </c>
-      <c r="I3" t="n">
-        <v>40</v>
       </c>
       <c r="J3" t="n">
         <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
         <v>23</v>
       </c>
       <c r="M3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N3" t="n">
         <v>25</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>23</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>22</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>23</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -603,51 +612,54 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="C4" t="n">
         <v>1984</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>2327</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2229</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1924</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2179</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2094</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1729</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2017</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1681</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1464</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1854</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1790</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1275</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1529</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1352</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1316</v>
       </c>
     </row>
@@ -658,51 +670,54 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3663</v>
+      </c>
+      <c r="C5" t="n">
         <v>3186</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>2634</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2950</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3335</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2854</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3332</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3557</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>3108</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>3991</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4589</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6786</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>7457</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>6004</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>4187</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1687</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>710</v>
       </c>
     </row>
@@ -713,51 +728,54 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1436</v>
+      </c>
+      <c r="C6" t="n">
         <v>1070</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>721</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>728</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>579</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>519</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>930</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1186</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>877</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1130</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1919</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>3066</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3160</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1237</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1048</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>507</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>398</v>
       </c>
     </row>
@@ -768,35 +786,35 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>438</v>
+      </c>
+      <c r="C7" t="n">
         <v>446</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>450</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>445</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>446</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>451</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>432</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>443</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>435</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>443</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -813,2323 +831,2452 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Expense and Other Assets, Current</t>
+          <t>Assets Held-for-sale, Not Part of Disposal Group</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>629</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>214</v>
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Assets, Current</t>
+          <t>Prepaid Expense and Other Assets, Current</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9016</v>
+        <v>832</v>
       </c>
       <c r="C9" t="n">
-        <v>8381</v>
+        <v>629</v>
       </c>
       <c r="D9" t="n">
-        <v>8484</v>
+        <v>647</v>
       </c>
       <c r="E9" t="n">
-        <v>8430</v>
+        <v>678</v>
       </c>
       <c r="F9" t="n">
-        <v>8531</v>
+        <v>596</v>
       </c>
       <c r="G9" t="n">
-        <v>9826</v>
+        <v>625</v>
       </c>
       <c r="H9" t="n">
-        <v>9433</v>
+        <v>411</v>
       </c>
       <c r="I9" t="n">
-        <v>10699</v>
+        <v>439</v>
       </c>
       <c r="J9" t="n">
-        <v>8911</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>9512</v>
+        <v>281</v>
       </c>
       <c r="L9" t="n">
-        <v>13145</v>
+        <v>346</v>
       </c>
       <c r="M9" t="n">
-        <v>15153</v>
+        <v>291</v>
       </c>
       <c r="N9" t="n">
-        <v>10913</v>
+        <v>231</v>
       </c>
       <c r="O9" t="n">
-        <v>7846</v>
+        <v>241</v>
       </c>
       <c r="P9" t="n">
-        <v>4749</v>
+        <v>231</v>
       </c>
       <c r="Q9" t="n">
-        <v>3688</v>
+        <v>250</v>
+      </c>
+      <c r="R9" t="n">
+        <v>214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Restricted Cash, Noncurrent</t>
+          <t>Assets, Current</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>10276</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9016</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8381</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>8484</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8430</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>8531</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>9826</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>9433</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>10699</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>8911</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>9512</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>13145</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>15153</v>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>10913</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>7846</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>4749</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Other Long-term Investments</t>
+          <t>Restricted Cash, Noncurrent</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5001</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>5008</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>4752</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>4476</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>4520</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>4310</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>4219</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>1857</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>1915</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>1832</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>1637</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>1715</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1952</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>1915</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>1912</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1803</v>
+        <v>16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Property, Plant and Equipment, Net</t>
+          <t>Other Long-term Investments</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19876</v>
+        <v>5331</v>
       </c>
       <c r="C12" t="n">
-        <v>17725</v>
+        <v>5001</v>
       </c>
       <c r="D12" t="n">
-        <v>17736</v>
+        <v>5008</v>
       </c>
       <c r="E12" t="n">
-        <v>17716</v>
+        <v>4752</v>
       </c>
       <c r="F12" t="n">
-        <v>18388</v>
+        <v>4476</v>
       </c>
       <c r="G12" t="n">
-        <v>18208</v>
+        <v>4520</v>
       </c>
       <c r="H12" t="n">
-        <v>18014</v>
+        <v>4310</v>
       </c>
       <c r="I12" t="n">
-        <v>12346</v>
+        <v>4219</v>
       </c>
       <c r="J12" t="n">
-        <v>12537</v>
+        <v>1857</v>
       </c>
       <c r="K12" t="n">
-        <v>12611</v>
+        <v>1915</v>
       </c>
       <c r="L12" t="n">
-        <v>12550</v>
+        <v>1832</v>
       </c>
       <c r="M12" t="n">
-        <v>12784</v>
+        <v>1637</v>
       </c>
       <c r="N12" t="n">
-        <v>12887</v>
+        <v>1715</v>
       </c>
       <c r="O12" t="n">
-        <v>13100</v>
+        <v>1952</v>
       </c>
       <c r="P12" t="n">
-        <v>13327</v>
+        <v>1915</v>
       </c>
       <c r="Q12" t="n">
-        <v>13392</v>
+        <v>1912</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1803</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Property, Plant and Equipment, Net</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2810</v>
+        <v>19944</v>
       </c>
       <c r="C13" t="n">
-        <v>2810</v>
+        <v>19876</v>
       </c>
       <c r="D13" t="n">
-        <v>2810</v>
+        <v>17725</v>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>17736</v>
       </c>
       <c r="F13" t="n">
-        <v>2802</v>
+        <v>17716</v>
       </c>
       <c r="G13" t="n">
-        <v>2922</v>
+        <v>18388</v>
       </c>
       <c r="H13" t="n">
-        <v>2877</v>
+        <v>18208</v>
       </c>
       <c r="I13" t="n">
-        <v>2583</v>
+        <v>18014</v>
       </c>
       <c r="J13" t="n">
-        <v>2583</v>
+        <v>12346</v>
       </c>
       <c r="K13" t="n">
-        <v>2583</v>
+        <v>12537</v>
       </c>
       <c r="L13" t="n">
-        <v>2583</v>
+        <v>12611</v>
       </c>
       <c r="M13" t="n">
-        <v>2583</v>
+        <v>12550</v>
       </c>
       <c r="N13" t="n">
-        <v>2583</v>
+        <v>12784</v>
       </c>
       <c r="O13" t="n">
-        <v>2583</v>
+        <v>12887</v>
       </c>
       <c r="P13" t="n">
-        <v>2583</v>
+        <v>13100</v>
       </c>
       <c r="Q13" t="n">
-        <v>2583</v>
+        <v>13327</v>
+      </c>
+      <c r="R13" t="n">
+        <v>13392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Intangible Assets, Net (Excluding Goodwill)</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2363</v>
+        <v>2810</v>
       </c>
       <c r="C14" t="n">
-        <v>2097</v>
+        <v>2810</v>
       </c>
       <c r="D14" t="n">
-        <v>2252</v>
+        <v>2810</v>
       </c>
       <c r="E14" t="n">
-        <v>2321</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="n">
-        <v>2157</v>
+        <v>2810</v>
       </c>
       <c r="G14" t="n">
-        <v>2263</v>
+        <v>2802</v>
       </c>
       <c r="H14" t="n">
-        <v>2278</v>
+        <v>2922</v>
       </c>
       <c r="I14" t="n">
-        <v>1883</v>
+        <v>2877</v>
       </c>
       <c r="J14" t="n">
-        <v>1912</v>
+        <v>2583</v>
       </c>
       <c r="K14" t="n">
-        <v>1940</v>
+        <v>2583</v>
       </c>
       <c r="L14" t="n">
-        <v>2002</v>
+        <v>2583</v>
       </c>
       <c r="M14" t="n">
-        <v>2042</v>
+        <v>2583</v>
       </c>
       <c r="N14" t="n">
-        <v>2158</v>
+        <v>2583</v>
       </c>
       <c r="O14" t="n">
-        <v>2229</v>
+        <v>2583</v>
       </c>
       <c r="P14" t="n">
-        <v>2290</v>
+        <v>2583</v>
       </c>
       <c r="Q14" t="n">
-        <v>2329</v>
+        <v>2583</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Derivative Instruments and Hedges, Noncurrent</t>
+          <t>Intangible Assets, Net (Excluding Goodwill)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>412</v>
+        <v>2286</v>
       </c>
       <c r="C15" t="n">
-        <v>604</v>
+        <v>2363</v>
       </c>
       <c r="D15" t="n">
-        <v>593</v>
+        <v>2097</v>
       </c>
       <c r="E15" t="n">
-        <v>769</v>
+        <v>2252</v>
       </c>
       <c r="F15" t="n">
-        <v>886</v>
+        <v>2321</v>
       </c>
       <c r="G15" t="n">
-        <v>922</v>
+        <v>2157</v>
       </c>
       <c r="H15" t="n">
-        <v>703</v>
+        <v>2263</v>
       </c>
       <c r="I15" t="n">
-        <v>743</v>
+        <v>2278</v>
       </c>
       <c r="J15" t="n">
-        <v>665</v>
+        <v>1883</v>
       </c>
       <c r="K15" t="n">
-        <v>763</v>
+        <v>1912</v>
       </c>
       <c r="L15" t="n">
-        <v>1062</v>
+        <v>1940</v>
       </c>
       <c r="M15" t="n">
-        <v>924</v>
+        <v>2002</v>
       </c>
       <c r="N15" t="n">
-        <v>545</v>
+        <v>2042</v>
       </c>
       <c r="O15" t="n">
-        <v>454</v>
+        <v>2158</v>
       </c>
       <c r="P15" t="n">
-        <v>332</v>
+        <v>2229</v>
       </c>
       <c r="Q15" t="n">
-        <v>347</v>
+        <v>2290</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Assets, Net</t>
+          <t>Derivative Instruments and Hedges, Noncurrent</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>412</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>604</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>593</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>886</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="I16" t="n">
-        <v>1239</v>
+        <v>703</v>
       </c>
       <c r="J16" t="n">
-        <v>1385</v>
+        <v>743</v>
       </c>
       <c r="K16" t="n">
-        <v>1475</v>
+        <v>665</v>
       </c>
       <c r="L16" t="n">
-        <v>1653</v>
+        <v>763</v>
       </c>
       <c r="M16" t="n">
-        <v>1818</v>
+        <v>1062</v>
       </c>
       <c r="N16" t="n">
-        <v>1400</v>
+        <v>924</v>
       </c>
       <c r="O16" t="n">
-        <v>1421</v>
+        <v>545</v>
       </c>
       <c r="P16" t="n">
-        <v>1464</v>
+        <v>454</v>
       </c>
       <c r="Q16" t="n">
-        <v>1361</v>
+        <v>332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Other Assets, Noncurrent</t>
+          <t>Deferred Income Tax Assets, Net</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1585</v>
+        <v>213</v>
       </c>
       <c r="C17" t="n">
-        <v>1380</v>
+        <v>239</v>
       </c>
       <c r="D17" t="n">
-        <v>1504</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>1691</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>479</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>495</v>
+        <v>1239</v>
       </c>
       <c r="K17" t="n">
-        <v>319</v>
+        <v>1385</v>
       </c>
       <c r="L17" t="n">
-        <v>494</v>
+        <v>1475</v>
       </c>
       <c r="M17" t="n">
-        <v>398</v>
+        <v>1653</v>
       </c>
       <c r="N17" t="n">
-        <v>344</v>
+        <v>1818</v>
       </c>
       <c r="O17" t="n">
-        <v>335</v>
+        <v>1400</v>
       </c>
       <c r="P17" t="n">
-        <v>300</v>
+        <v>1421</v>
       </c>
       <c r="Q17" t="n">
-        <v>322</v>
+        <v>1464</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Other Assets, Noncurrent</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41308</v>
+        <v>1404</v>
       </c>
       <c r="C18" t="n">
-        <v>38020</v>
+        <v>1585</v>
       </c>
       <c r="D18" t="n">
-        <v>38146</v>
+        <v>1380</v>
       </c>
       <c r="E18" t="n">
-        <v>38228</v>
+        <v>1504</v>
       </c>
       <c r="F18" t="n">
-        <v>37878</v>
+        <v>1691</v>
       </c>
       <c r="G18" t="n">
-        <v>39125</v>
+        <v>479</v>
       </c>
       <c r="H18" t="n">
-        <v>38178</v>
+        <v>589</v>
       </c>
       <c r="I18" t="n">
-        <v>31945</v>
+        <v>578</v>
       </c>
       <c r="J18" t="n">
-        <v>30472</v>
+        <v>527</v>
       </c>
       <c r="K18" t="n">
-        <v>31117</v>
+        <v>495</v>
       </c>
       <c r="L18" t="n">
-        <v>35175</v>
+        <v>319</v>
       </c>
       <c r="M18" t="n">
-        <v>37468</v>
+        <v>494</v>
       </c>
       <c r="N18" t="n">
-        <v>32833</v>
+        <v>398</v>
       </c>
       <c r="O18" t="n">
-        <v>29932</v>
+        <v>344</v>
       </c>
       <c r="P18" t="n">
-        <v>27015</v>
+        <v>335</v>
       </c>
       <c r="Q18" t="n">
-        <v>25886</v>
+        <v>300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Short-term Debt</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>42603</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>41308</v>
       </c>
       <c r="D19" t="n">
-        <v>861</v>
+        <v>38020</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>38146</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>38228</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>37878</v>
       </c>
       <c r="H19" t="n">
-        <v>500</v>
+        <v>39125</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>38178</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>31945</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>30472</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>31117</v>
       </c>
       <c r="M19" t="n">
-        <v>1300</v>
+        <v>35175</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>37468</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>32833</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>29932</v>
       </c>
       <c r="Q19" t="n">
-        <v>1300</v>
+        <v>27015</v>
+      </c>
+      <c r="R19" t="n">
+        <v>25886</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Accounts Receivable Securitization Program Amounts Borrowed</t>
+          <t>Short-term Debt</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1125</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1082</v>
+        <v>861</v>
       </c>
       <c r="F20" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="O20" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>725</v>
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Long-term Debt and Lease Obligation, Current</t>
+          <t>Accounts Receivable Securitization Program Amounts Borrowed</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1899</v>
+        <v>300</v>
       </c>
       <c r="C21" t="n">
-        <v>231</v>
+        <v>750</v>
       </c>
       <c r="D21" t="n">
-        <v>230</v>
+        <v>1225</v>
       </c>
       <c r="E21" t="n">
-        <v>882</v>
+        <v>1125</v>
       </c>
       <c r="F21" t="n">
-        <v>785</v>
+        <v>1082</v>
       </c>
       <c r="G21" t="n">
-        <v>1939</v>
+        <v>750</v>
       </c>
       <c r="H21" t="n">
-        <v>54</v>
+        <v>750</v>
       </c>
       <c r="I21" t="n">
-        <v>1935</v>
+        <v>875</v>
       </c>
       <c r="J21" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="M21" t="n">
-        <v>41</v>
+        <v>625</v>
       </c>
       <c r="N21" t="n">
-        <v>124</v>
+        <v>725</v>
       </c>
       <c r="O21" t="n">
-        <v>382</v>
+        <v>500</v>
       </c>
       <c r="P21" t="n">
-        <v>511</v>
+        <v>475</v>
       </c>
       <c r="Q21" t="n">
-        <v>480</v>
+        <v>661</v>
+      </c>
+      <c r="R21" t="n">
+        <v>725</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Forward Repurchase Obligation To Be Paid Current</t>
+          <t>Long-term Debt and Lease Obligation, Current</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>641</v>
+        <v>1876</v>
       </c>
       <c r="C22" t="n">
-        <v>701</v>
+        <v>1899</v>
       </c>
       <c r="D22" t="n">
-        <v>682</v>
+        <v>231</v>
       </c>
       <c r="E22" t="n">
-        <v>723</v>
+        <v>230</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1939</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>511</v>
+      </c>
+      <c r="R22" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payable, Current</t>
+          <t>Forward Repurchase Obligation To Be Paid Current</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1359</v>
+        <v>613</v>
       </c>
       <c r="C23" t="n">
-        <v>1362</v>
+        <v>641</v>
       </c>
       <c r="D23" t="n">
-        <v>1276</v>
+        <v>701</v>
       </c>
       <c r="E23" t="n">
-        <v>1328</v>
+        <v>682</v>
       </c>
       <c r="F23" t="n">
-        <v>1291</v>
+        <v>723</v>
       </c>
       <c r="G23" t="n">
-        <v>1317</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1124</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1076</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1005</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1398</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1472</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1172</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1129</v>
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Derivative Instruments and Hedges, Liabilities</t>
+          <t>Accounts Payable, Current</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4209</v>
+        <v>1504</v>
       </c>
       <c r="C24" t="n">
-        <v>3610</v>
+        <v>1359</v>
       </c>
       <c r="D24" t="n">
-        <v>4086</v>
+        <v>1362</v>
       </c>
       <c r="E24" t="n">
-        <v>4646</v>
+        <v>1276</v>
       </c>
       <c r="F24" t="n">
-        <v>3563</v>
+        <v>1328</v>
       </c>
       <c r="G24" t="n">
-        <v>4930</v>
+        <v>1291</v>
       </c>
       <c r="H24" t="n">
-        <v>5214</v>
+        <v>1317</v>
       </c>
       <c r="I24" t="n">
-        <v>4560</v>
+        <v>1100</v>
       </c>
       <c r="J24" t="n">
-        <v>5076</v>
+        <v>1124</v>
       </c>
       <c r="K24" t="n">
-        <v>5646</v>
+        <v>1076</v>
       </c>
       <c r="L24" t="n">
-        <v>8796</v>
+        <v>1005</v>
       </c>
       <c r="M24" t="n">
-        <v>9934</v>
+        <v>1398</v>
       </c>
       <c r="N24" t="n">
-        <v>6835</v>
+        <v>1472</v>
       </c>
       <c r="O24" t="n">
-        <v>4948</v>
+        <v>1284</v>
       </c>
       <c r="P24" t="n">
-        <v>2044</v>
+        <v>1172</v>
       </c>
       <c r="Q24" t="n">
-        <v>868</v>
+        <v>1078</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>vistra_MarginDepositLiabilities</t>
+          <t>Derivative Instruments and Hedges, Liabilities</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>4893</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4209</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>3610</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4086</v>
       </c>
       <c r="F25" t="n">
-        <v>175</v>
+        <v>4646</v>
       </c>
       <c r="G25" t="n">
-        <v>164</v>
+        <v>3563</v>
       </c>
       <c r="H25" t="n">
-        <v>115</v>
+        <v>4930</v>
       </c>
       <c r="I25" t="n">
-        <v>50</v>
+        <v>5214</v>
       </c>
       <c r="J25" t="n">
-        <v>46</v>
+        <v>4560</v>
       </c>
       <c r="K25" t="n">
-        <v>48</v>
+        <v>5076</v>
       </c>
       <c r="L25" t="n">
-        <v>37</v>
+        <v>5646</v>
       </c>
       <c r="M25" t="n">
-        <v>43</v>
+        <v>8796</v>
       </c>
       <c r="N25" t="n">
-        <v>223</v>
+        <v>9934</v>
       </c>
       <c r="O25" t="n">
-        <v>57</v>
+        <v>6835</v>
       </c>
       <c r="P25" t="n">
-        <v>43</v>
+        <v>4948</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>2044</v>
+      </c>
+      <c r="R25" t="n">
+        <v>868</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Accrual for Taxes Other than Income Taxes, Current</t>
+          <t>vistra_MarginDepositLiabilities</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C26" t="n">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>199</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H26" t="n">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="I26" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="J26" t="n">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="L26" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="N26" t="n">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="O26" t="n">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="P26" t="n">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="Q26" t="n">
-        <v>99</v>
+        <v>43</v>
+      </c>
+      <c r="R26" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Interest Payable, Current</t>
+          <t>Accrued Income Taxes, Current</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>287</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>55</v>
+        <v>8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Asset Retirement Obligation, Current</t>
+          <t>Accrual for Taxes Other than Income Taxes, Current</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="C28" t="n">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="D28" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E28" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F28" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G28" t="n">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="H28" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="I28" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J28" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="K28" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L28" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="M28" t="n">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="N28" t="n">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="O28" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" t="n">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="Q28" t="n">
+        <v>143</v>
+      </c>
+      <c r="R28" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Other Liabilities, Current</t>
+          <t>Interest Payable, Current</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>604</v>
+        <v>249</v>
       </c>
       <c r="C29" t="n">
-        <v>687</v>
+        <v>287</v>
       </c>
       <c r="D29" t="n">
-        <v>694</v>
+        <v>225</v>
       </c>
       <c r="E29" t="n">
-        <v>606</v>
+        <v>188</v>
       </c>
       <c r="F29" t="n">
-        <v>560</v>
+        <v>244</v>
       </c>
       <c r="G29" t="n">
-        <v>443</v>
+        <v>222</v>
       </c>
       <c r="H29" t="n">
-        <v>461</v>
+        <v>215</v>
       </c>
       <c r="I29" t="n">
-        <v>674</v>
+        <v>208</v>
       </c>
       <c r="J29" t="n">
-        <v>563</v>
+        <v>113</v>
       </c>
       <c r="K29" t="n">
-        <v>458</v>
+        <v>156</v>
       </c>
       <c r="L29" t="n">
-        <v>616</v>
+        <v>113</v>
       </c>
       <c r="M29" t="n">
-        <v>565</v>
+        <v>112</v>
       </c>
       <c r="N29" t="n">
-        <v>600</v>
+        <v>156</v>
       </c>
       <c r="O29" t="n">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="P29" t="n">
-        <v>487</v>
+        <v>76</v>
       </c>
       <c r="Q29" t="n">
-        <v>554</v>
+        <v>138</v>
+      </c>
+      <c r="R29" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Liabilities, Current</t>
+          <t>Asset Retirement Obligation, Current</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10059</v>
+        <v>197</v>
       </c>
       <c r="C30" t="n">
-        <v>8426</v>
+        <v>185</v>
       </c>
       <c r="D30" t="n">
-        <v>9434</v>
+        <v>202</v>
       </c>
       <c r="E30" t="n">
-        <v>9753</v>
+        <v>146</v>
       </c>
       <c r="F30" t="n">
-        <v>7660</v>
+        <v>136</v>
       </c>
       <c r="G30" t="n">
-        <v>10057</v>
+        <v>102</v>
       </c>
       <c r="H30" t="n">
-        <v>8775</v>
+        <v>106</v>
       </c>
       <c r="I30" t="n">
-        <v>8748</v>
+        <v>119</v>
       </c>
       <c r="J30" t="n">
-        <v>7626</v>
+        <v>123</v>
       </c>
       <c r="K30" t="n">
-        <v>8162</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
-        <v>11911</v>
+        <v>139</v>
       </c>
       <c r="M30" t="n">
-        <v>14499</v>
+        <v>121</v>
       </c>
       <c r="N30" t="n">
-        <v>9865</v>
+        <v>112</v>
       </c>
       <c r="O30" t="n">
-        <v>7922</v>
+        <v>104</v>
       </c>
       <c r="P30" t="n">
-        <v>5223</v>
+        <v>110</v>
       </c>
       <c r="Q30" t="n">
-        <v>5406</v>
+        <v>103</v>
+      </c>
+      <c r="R30" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Long-term Debt and Lease Obligation</t>
+          <t>Disposal Group, Including Discontinued Operation, Liabilities</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17264</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
-        <v>15757</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>15540</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>15423</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>13945</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>13947</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>14693</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>11758</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>11530</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>11930</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>11947</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>10473</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>10493</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>10484</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9312</v>
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Derivative And Hedge Liabilities Noncurrent</t>
+          <t>Other Liabilities, Current</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1256</v>
+        <v>662</v>
       </c>
       <c r="C32" t="n">
-        <v>1388</v>
+        <v>604</v>
       </c>
       <c r="D32" t="n">
-        <v>1430</v>
+        <v>687</v>
       </c>
       <c r="E32" t="n">
-        <v>1459</v>
+        <v>694</v>
       </c>
       <c r="F32" t="n">
-        <v>1141</v>
+        <v>606</v>
       </c>
       <c r="G32" t="n">
-        <v>2095</v>
+        <v>560</v>
       </c>
       <c r="H32" t="n">
-        <v>1892</v>
+        <v>443</v>
       </c>
       <c r="I32" t="n">
-        <v>1576</v>
+        <v>461</v>
       </c>
       <c r="J32" t="n">
-        <v>1554</v>
+        <v>674</v>
       </c>
       <c r="K32" t="n">
-        <v>1794</v>
+        <v>563</v>
       </c>
       <c r="L32" t="n">
-        <v>1803</v>
+        <v>458</v>
       </c>
       <c r="M32" t="n">
-        <v>1650</v>
+        <v>616</v>
       </c>
       <c r="N32" t="n">
-        <v>1108</v>
+        <v>565</v>
       </c>
       <c r="O32" t="n">
-        <v>896</v>
+        <v>600</v>
       </c>
       <c r="P32" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="Q32" t="n">
-        <v>441</v>
+        <v>487</v>
+      </c>
+      <c r="R32" t="n">
+        <v>554</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Liabilities, Net</t>
+          <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1201</v>
+        <v>10557</v>
       </c>
       <c r="C33" t="n">
-        <v>765</v>
+        <v>10059</v>
       </c>
       <c r="D33" t="n">
-        <v>569</v>
+        <v>8426</v>
       </c>
       <c r="E33" t="n">
-        <v>512</v>
+        <v>9434</v>
       </c>
       <c r="F33" t="n">
-        <v>839</v>
+        <v>9753</v>
       </c>
       <c r="G33" t="n">
-        <v>250</v>
+        <v>7660</v>
       </c>
       <c r="H33" t="n">
-        <v>118</v>
+        <v>10057</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>8775</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>8748</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>7626</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>8162</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>11911</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>14499</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>9865</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>7922</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>5223</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5406</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Asset Retirement Obligations, Noncurrent</t>
+          <t>Long-term Debt and Lease Obligation</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4046</v>
+        <v>17719</v>
       </c>
       <c r="C34" t="n">
-        <v>3944</v>
+        <v>17264</v>
       </c>
       <c r="D34" t="n">
-        <v>3953</v>
+        <v>15757</v>
       </c>
       <c r="E34" t="n">
-        <v>3937</v>
+        <v>15540</v>
       </c>
       <c r="F34" t="n">
-        <v>3884</v>
+        <v>15423</v>
       </c>
       <c r="G34" t="n">
-        <v>3847</v>
+        <v>13945</v>
       </c>
       <c r="H34" t="n">
-        <v>3806</v>
+        <v>13947</v>
       </c>
       <c r="I34" t="n">
-        <v>2350</v>
+        <v>14693</v>
       </c>
       <c r="J34" t="n">
-        <v>2334</v>
+        <v>11758</v>
       </c>
       <c r="K34" t="n">
-        <v>2308</v>
+        <v>11530</v>
       </c>
       <c r="L34" t="n">
-        <v>2340</v>
+        <v>11930</v>
       </c>
       <c r="M34" t="n">
-        <v>2338</v>
+        <v>11947</v>
       </c>
       <c r="N34" t="n">
-        <v>2347</v>
+        <v>11949</v>
       </c>
       <c r="O34" t="n">
-        <v>2326</v>
+        <v>10473</v>
       </c>
       <c r="P34" t="n">
-        <v>2346</v>
+        <v>10493</v>
       </c>
       <c r="Q34" t="n">
-        <v>2337</v>
+        <v>10484</v>
+      </c>
+      <c r="R34" t="n">
+        <v>9312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Other Liabilities, Noncurrent</t>
+          <t>Derivative And Hedge Liabilities Noncurrent</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1426</v>
+        <v>1458</v>
       </c>
       <c r="C35" t="n">
-        <v>1454</v>
+        <v>1256</v>
       </c>
       <c r="D35" t="n">
-        <v>1326</v>
+        <v>1388</v>
       </c>
       <c r="E35" t="n">
-        <v>1228</v>
+        <v>1430</v>
       </c>
       <c r="F35" t="n">
-        <v>1191</v>
+        <v>1459</v>
       </c>
       <c r="G35" t="n">
-        <v>1112</v>
+        <v>1141</v>
       </c>
       <c r="H35" t="n">
-        <v>1096</v>
+        <v>2095</v>
       </c>
       <c r="I35" t="n">
-        <v>867</v>
+        <v>1892</v>
       </c>
       <c r="J35" t="n">
-        <v>970</v>
+        <v>1576</v>
       </c>
       <c r="K35" t="n">
-        <v>1083</v>
+        <v>1554</v>
       </c>
       <c r="L35" t="n">
-        <v>1117</v>
+        <v>1794</v>
       </c>
       <c r="M35" t="n">
-        <v>1083</v>
+        <v>1803</v>
       </c>
       <c r="N35" t="n">
-        <v>1226</v>
+        <v>1650</v>
       </c>
       <c r="O35" t="n">
-        <v>1814</v>
+        <v>1108</v>
       </c>
       <c r="P35" t="n">
-        <v>1867</v>
+        <v>896</v>
       </c>
       <c r="Q35" t="n">
-        <v>1848</v>
+        <v>537</v>
+      </c>
+      <c r="R35" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Deferred Income Tax Liabilities, Net</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35698</v>
+        <v>1271</v>
       </c>
       <c r="C36" t="n">
-        <v>32797</v>
+        <v>1201</v>
       </c>
       <c r="D36" t="n">
-        <v>33310</v>
+        <v>765</v>
       </c>
       <c r="E36" t="n">
-        <v>33390</v>
+        <v>569</v>
       </c>
       <c r="F36" t="n">
-        <v>29225</v>
+        <v>512</v>
       </c>
       <c r="G36" t="n">
-        <v>31818</v>
+        <v>839</v>
       </c>
       <c r="H36" t="n">
-        <v>30894</v>
+        <v>250</v>
       </c>
       <c r="I36" t="n">
-        <v>26424</v>
+        <v>118</v>
       </c>
       <c r="J36" t="n">
-        <v>25098</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>25901</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>29574</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>32065</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>25531</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>23901</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>20947</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>19793</v>
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Preferred Stock, Value, Issued</t>
+          <t>Asset Retirement Obligations, Noncurrent</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2476</v>
+        <v>4072</v>
       </c>
       <c r="C37" t="n">
-        <v>2476</v>
+        <v>4046</v>
       </c>
       <c r="D37" t="n">
-        <v>2476</v>
+        <v>3944</v>
       </c>
       <c r="E37" t="n">
-        <v>2476</v>
+        <v>3953</v>
       </c>
       <c r="F37" t="n">
-        <v>2476</v>
+        <v>3937</v>
       </c>
       <c r="G37" t="n">
-        <v>2476</v>
+        <v>3884</v>
       </c>
       <c r="H37" t="n">
-        <v>2476</v>
+        <v>3847</v>
       </c>
       <c r="I37" t="n">
-        <v>2000</v>
+        <v>3806</v>
       </c>
       <c r="J37" t="n">
-        <v>2000</v>
+        <v>2350</v>
       </c>
       <c r="K37" t="n">
-        <v>2000</v>
+        <v>2334</v>
       </c>
       <c r="L37" t="n">
-        <v>2000</v>
+        <v>2308</v>
       </c>
       <c r="M37" t="n">
-        <v>2000</v>
+        <v>2340</v>
       </c>
       <c r="N37" t="n">
-        <v>2000</v>
+        <v>2338</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2347</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2326</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2346</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2337</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Common Stock, Value, Issued</t>
+          <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>1594</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>1426</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>1454</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>1326</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>1228</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>1191</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>1112</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>1096</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>867</v>
       </c>
       <c r="K38" t="n">
-        <v>5</v>
+        <v>970</v>
       </c>
       <c r="L38" t="n">
-        <v>5</v>
+        <v>1083</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>1117</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1083</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>1226</v>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>1814</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>1867</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1848</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Treasury Stock, Common, Value</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-7303</v>
+        <v>37109</v>
       </c>
       <c r="C39" t="n">
-        <v>-6675</v>
+        <v>35698</v>
       </c>
       <c r="D39" t="n">
-        <v>-6485</v>
+        <v>32797</v>
       </c>
       <c r="E39" t="n">
-        <v>-6248</v>
+        <v>33310</v>
       </c>
       <c r="F39" t="n">
-        <v>-5684</v>
+        <v>33390</v>
       </c>
       <c r="G39" t="n">
-        <v>-5278</v>
+        <v>29225</v>
       </c>
       <c r="H39" t="n">
-        <v>-4947</v>
+        <v>31818</v>
       </c>
       <c r="I39" t="n">
-        <v>-4278</v>
+        <v>30894</v>
       </c>
       <c r="J39" t="n">
-        <v>-3955</v>
+        <v>26424</v>
       </c>
       <c r="K39" t="n">
-        <v>-3706</v>
+        <v>25098</v>
       </c>
       <c r="L39" t="n">
-        <v>-3052</v>
+        <v>25901</v>
       </c>
       <c r="M39" t="n">
-        <v>-2645</v>
+        <v>29574</v>
       </c>
       <c r="N39" t="n">
-        <v>-2170</v>
+        <v>32065</v>
       </c>
       <c r="O39" t="n">
-        <v>-1148</v>
+        <v>25531</v>
       </c>
       <c r="P39" t="n">
-        <v>-1148</v>
+        <v>23901</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1148</v>
+        <v>20947</v>
+      </c>
+      <c r="R39" t="n">
+        <v>19793</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Additional Paid in Capital, Common Stock</t>
+          <t>Preferred Stock, Value, Issued</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9499</v>
+        <v>2476</v>
       </c>
       <c r="C40" t="n">
-        <v>9491</v>
+        <v>2476</v>
       </c>
       <c r="D40" t="n">
-        <v>9450</v>
+        <v>2476</v>
       </c>
       <c r="E40" t="n">
-        <v>9407</v>
+        <v>2476</v>
       </c>
       <c r="F40" t="n">
-        <v>9396</v>
+        <v>2476</v>
       </c>
       <c r="G40" t="n">
-        <v>10917</v>
+        <v>2476</v>
       </c>
       <c r="H40" t="n">
-        <v>10878</v>
+        <v>2476</v>
       </c>
       <c r="I40" t="n">
-        <v>10075</v>
+        <v>2476</v>
       </c>
       <c r="J40" t="n">
-        <v>9993</v>
+        <v>2000</v>
       </c>
       <c r="K40" t="n">
-        <v>9952</v>
+        <v>2000</v>
       </c>
       <c r="L40" t="n">
-        <v>9923</v>
+        <v>2000</v>
       </c>
       <c r="M40" t="n">
-        <v>9890</v>
+        <v>2000</v>
       </c>
       <c r="N40" t="n">
-        <v>9844</v>
+        <v>2000</v>
       </c>
       <c r="O40" t="n">
-        <v>9829</v>
+        <v>2000</v>
       </c>
       <c r="P40" t="n">
-        <v>9816</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9805</v>
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Retained Earnings (Accumulated Deficit)</t>
+          <t>Common Stock, Value, Issued</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>903</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>-107</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>-642</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>-835</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>-759</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>-2533</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>-2762</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>-2306</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>-2696</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>-3058</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
-        <v>-3284</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>-3842</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>-2363</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>-2619</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-2552</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>-2516</v>
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
+          <t>Treasury Stock, Common, Value</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17</v>
+        <v>-7627</v>
       </c>
       <c r="C42" t="n">
-        <v>20</v>
+        <v>-7303</v>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>-6675</v>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>-6485</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>-6248</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>-5684</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>-5278</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>-4947</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>-4278</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>-3955</v>
       </c>
       <c r="L42" t="n">
-        <v>-10</v>
+        <v>-3706</v>
       </c>
       <c r="M42" t="n">
-        <v>-16</v>
+        <v>-3052</v>
       </c>
       <c r="N42" t="n">
-        <v>-16</v>
+        <v>-2645</v>
       </c>
       <c r="O42" t="n">
-        <v>-31</v>
+        <v>-2170</v>
       </c>
       <c r="P42" t="n">
-        <v>-45</v>
+        <v>-1148</v>
       </c>
       <c r="Q42" t="n">
-        <v>-46</v>
+        <v>-1148</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-1148</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Total Shareholders Equity</t>
+          <t>Additional Paid in Capital, Common Stock</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5597</v>
+        <v>9536</v>
       </c>
       <c r="C43" t="n">
-        <v>5210</v>
+        <v>9499</v>
       </c>
       <c r="D43" t="n">
-        <v>4823</v>
+        <v>9491</v>
       </c>
       <c r="E43" t="n">
-        <v>4825</v>
+        <v>9450</v>
       </c>
       <c r="F43" t="n">
-        <v>5441</v>
+        <v>9407</v>
       </c>
       <c r="G43" t="n">
-        <v>5593</v>
+        <v>9396</v>
       </c>
       <c r="H43" t="n">
-        <v>5656</v>
+        <v>10917</v>
       </c>
       <c r="I43" t="n">
-        <v>5506</v>
+        <v>10878</v>
       </c>
       <c r="J43" t="n">
-        <v>5359</v>
+        <v>10075</v>
       </c>
       <c r="K43" t="n">
-        <v>5201</v>
+        <v>9993</v>
       </c>
       <c r="L43" t="n">
-        <v>5582</v>
+        <v>9952</v>
       </c>
       <c r="M43" t="n">
-        <v>5392</v>
+        <v>9923</v>
       </c>
       <c r="N43" t="n">
-        <v>7300</v>
+        <v>9890</v>
       </c>
       <c r="O43" t="n">
-        <v>6036</v>
+        <v>9844</v>
       </c>
       <c r="P43" t="n">
-        <v>6076</v>
+        <v>9829</v>
       </c>
       <c r="Q43" t="n">
-        <v>6100</v>
+        <v>9816</v>
+      </c>
+      <c r="R43" t="n">
+        <v>9805</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Stockholders' Equity Attributable to Noncontrolling Interest</t>
+          <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>1076</v>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>903</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>-107</v>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>-642</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>-835</v>
       </c>
       <c r="G44" t="n">
-        <v>1714</v>
+        <v>-759</v>
       </c>
       <c r="H44" t="n">
-        <v>1628</v>
+        <v>-2533</v>
       </c>
       <c r="I44" t="n">
-        <v>15</v>
+        <v>-2762</v>
       </c>
       <c r="J44" t="n">
-        <v>15</v>
+        <v>-2306</v>
       </c>
       <c r="K44" t="n">
-        <v>15</v>
+        <v>-2696</v>
       </c>
       <c r="L44" t="n">
-        <v>19</v>
+        <v>-3058</v>
       </c>
       <c r="M44" t="n">
-        <v>11</v>
+        <v>-3284</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>-3842</v>
       </c>
       <c r="O44" t="n">
-        <v>-5</v>
+        <v>-2363</v>
       </c>
       <c r="P44" t="n">
-        <v>-8</v>
+        <v>-2619</v>
       </c>
       <c r="Q44" t="n">
-        <v>-7</v>
+        <v>-2552</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-2516</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Stockholders' Equity, Including Portion Attributable to Noncontrolling Interest</t>
+          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5610</v>
+        <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>5223</v>
+        <v>17</v>
       </c>
       <c r="D45" t="n">
-        <v>4836</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>4838</v>
+        <v>19</v>
       </c>
       <c r="F45" t="n">
-        <v>5455</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>7307</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>7284</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>5521</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>5374</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>5216</v>
+        <v>12</v>
       </c>
       <c r="L45" t="n">
-        <v>5601</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
-        <v>5403</v>
+        <v>-10</v>
       </c>
       <c r="N45" t="n">
-        <v>7302</v>
+        <v>-16</v>
       </c>
       <c r="O45" t="n">
-        <v>6031</v>
+        <v>-16</v>
       </c>
       <c r="P45" t="n">
-        <v>6068</v>
+        <v>-31</v>
       </c>
       <c r="Q45" t="n">
-        <v>6093</v>
+        <v>-45</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Inventory, Net</t>
+          <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>603</v>
+        <v>5482</v>
       </c>
       <c r="C46" t="n">
-        <v>970</v>
+        <v>5597</v>
       </c>
       <c r="D46" t="n">
-        <v>965</v>
+        <v>5210</v>
       </c>
       <c r="E46" t="n">
-        <v>960</v>
+        <v>4823</v>
       </c>
       <c r="F46" t="n">
-        <v>949</v>
+        <v>4825</v>
       </c>
       <c r="G46" t="n">
-        <v>964</v>
+        <v>5441</v>
       </c>
       <c r="H46" t="n">
-        <v>976</v>
+        <v>5593</v>
       </c>
       <c r="I46" t="n">
-        <v>685</v>
+        <v>5656</v>
       </c>
       <c r="J46" t="n">
-        <v>676</v>
+        <v>5506</v>
       </c>
       <c r="K46" t="n">
-        <v>629</v>
+        <v>5359</v>
       </c>
       <c r="L46" t="n">
-        <v>590</v>
+        <v>5201</v>
       </c>
       <c r="M46" t="n">
-        <v>601</v>
+        <v>5582</v>
       </c>
       <c r="N46" t="n">
-        <v>546</v>
+        <v>5392</v>
       </c>
       <c r="O46" t="n">
-        <v>471</v>
+        <v>7300</v>
       </c>
       <c r="P46" t="n">
-        <v>486</v>
+        <v>6036</v>
       </c>
       <c r="Q46" t="n">
-        <v>467</v>
+        <v>6076</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Forward Repurchase Obligation To Be Paid Noncurrent</t>
+          <t>Stockholders' Equity Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>613</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>613</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
-        <v>632</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1628</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Receivable, Current</t>
+          <t>Stockholders' Equity, Including Portion Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>5494</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>5610</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>5223</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>4836</v>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>4838</v>
       </c>
       <c r="G48" t="n">
-        <v>16</v>
+        <v>5455</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>7307</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>7284</v>
       </c>
       <c r="J48" t="n">
-        <v>26</v>
+        <v>5521</v>
       </c>
       <c r="K48" t="n">
-        <v>24</v>
+        <v>5374</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>5216</v>
       </c>
       <c r="M48" t="n">
-        <v>18</v>
+        <v>5601</v>
       </c>
       <c r="N48" t="n">
-        <v>21</v>
+        <v>5403</v>
       </c>
       <c r="O48" t="n">
-        <v>7</v>
+        <v>7302</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>6031</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6068</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6093</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Right-of-Use Asset</t>
+          <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="F49" t="n">
-        <v>109</v>
+        <v>960</v>
       </c>
       <c r="G49" t="n">
-        <v>71</v>
+        <v>949</v>
       </c>
       <c r="H49" t="n">
-        <v>62</v>
+        <v>964</v>
       </c>
       <c r="I49" t="n">
-        <v>53</v>
+        <v>976</v>
       </c>
       <c r="J49" t="n">
-        <v>54</v>
+        <v>685</v>
       </c>
       <c r="K49" t="n">
-        <v>50</v>
+        <v>676</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>629</v>
       </c>
       <c r="M49" t="n">
-        <v>40</v>
+        <v>590</v>
       </c>
       <c r="N49" t="n">
-        <v>39</v>
+        <v>601</v>
       </c>
       <c r="O49" t="n">
-        <v>35</v>
+        <v>546</v>
       </c>
       <c r="P49" t="n">
-        <v>42</v>
+        <v>471</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>486</v>
+      </c>
+      <c r="R49" t="n">
+        <v>467</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Liability, Current</t>
+          <t>Forward Repurchase Obligation To Be Paid Noncurrent</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3139,52 +3286,55 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>632</v>
       </c>
       <c r="G50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Liability, Noncurrent</t>
+          <t>Income Taxes Receivable, Current</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3200,46 +3350,49 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="M51" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="O51" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="P51" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Tax Receivable Agreement Obligation Noncurrent</t>
+          <t>Operating Lease, Right-of-Use Asset</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3255,46 +3408,49 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="I52" t="n">
-        <v>640</v>
+        <v>62</v>
       </c>
       <c r="J52" t="n">
-        <v>591</v>
+        <v>53</v>
       </c>
       <c r="K52" t="n">
-        <v>578</v>
+        <v>54</v>
       </c>
       <c r="L52" t="n">
-        <v>423</v>
+        <v>50</v>
       </c>
       <c r="M52" t="n">
-        <v>509</v>
+        <v>39</v>
       </c>
       <c r="N52" t="n">
-        <v>475</v>
+        <v>40</v>
       </c>
       <c r="O52" t="n">
-        <v>416</v>
+        <v>39</v>
       </c>
       <c r="P52" t="n">
-        <v>451</v>
+        <v>35</v>
       </c>
       <c r="Q52" t="n">
-        <v>410</v>
+        <v>42</v>
+      </c>
+      <c r="R52" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Operating Lease, Liability, Current</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3313,43 +3469,46 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>544</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Accrued Income Taxes, Current</t>
+          <t>Operating Lease, Liability, Noncurrent</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3368,37 +3527,156 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L54" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>38</v>
+      </c>
+      <c r="R54" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Tax Receivable Agreement Obligation Noncurrent</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" t="n">
+        <v>15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" t="n">
+        <v>640</v>
+      </c>
+      <c r="K55" t="n">
+        <v>591</v>
+      </c>
+      <c r="L55" t="n">
+        <v>578</v>
+      </c>
+      <c r="M55" t="n">
+        <v>423</v>
+      </c>
+      <c r="N55" t="n">
+        <v>509</v>
+      </c>
+      <c r="O55" t="n">
+        <v>475</v>
+      </c>
+      <c r="P55" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>451</v>
+      </c>
+      <c r="R55" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>544</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3412,56 +3690,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -3472,51 +3753,54 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4017</v>
+      </c>
+      <c r="C2" t="n">
         <v>5640</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>4971</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>4250</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>3933</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6288</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>3845</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>3054</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>4086</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3189</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4425</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>5146</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1588</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>3125</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2991</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2565</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3207</v>
       </c>
     </row>
@@ -3527,51 +3811,54 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>-1774</v>
+      </c>
+      <c r="C3" t="n">
         <v>-2530</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>-2370</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>-1974</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>-2447</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>-2207</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-1597</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>-1716</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>-2109</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-1475</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>-2170</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>-3139</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>-2162</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>-2279</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>-1763</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>-1320</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>-4745</v>
       </c>
     </row>
@@ -3582,51 +3869,54 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>-853</v>
+      </c>
+      <c r="C4" t="n">
         <v>-700</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>-655</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>-733</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-693</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>-616</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-628</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-498</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-411</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-445</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-421</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>-400</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>-435</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>-416</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>-372</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>-429</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>-371</v>
       </c>
     </row>
@@ -3637,51 +3927,54 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-445</v>
+      </c>
+      <c r="C5" t="n">
         <v>-484</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>-460</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-541</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-522</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-466</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-437</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-403</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-375</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-369</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-366</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-390</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-394</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-430</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-468</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>-464</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>-423</v>
       </c>
     </row>
@@ -3692,755 +3985,794 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-392</v>
+      </c>
+      <c r="C6" t="n">
         <v>-427</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-444</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-419</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-391</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-411</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-375</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-351</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-357</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-309</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-288</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-323</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-280</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-288</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-269</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-252</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Impairment of Long-Lived Assets Held-for-use</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>-5</v>
       </c>
       <c r="E7" t="n">
-        <v>-120</v>
+        <v>-68</v>
       </c>
       <c r="F7" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>834</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1131</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>894</v>
+        <v>-49</v>
       </c>
       <c r="M7" t="n">
-        <v>-1683</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-288</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2583</v>
+        <v>-38</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Other Nonoperating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-24</v>
+        <v>553</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1037</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="F8" t="n">
-        <v>-3</v>
+        <v>-120</v>
       </c>
       <c r="G8" t="n">
-        <v>-3</v>
+        <v>2588</v>
       </c>
       <c r="H8" t="n">
-        <v>-4</v>
+        <v>808</v>
       </c>
       <c r="I8" t="n">
-        <v>-3</v>
+        <v>86</v>
       </c>
       <c r="J8" t="n">
-        <v>-2</v>
+        <v>834</v>
       </c>
       <c r="K8" t="n">
-        <v>-3</v>
+        <v>591</v>
       </c>
       <c r="L8" t="n">
-        <v>-5</v>
+        <v>1131</v>
       </c>
       <c r="M8" t="n">
-        <v>-9</v>
+        <v>894</v>
       </c>
       <c r="N8" t="n">
-        <v>-4</v>
+        <v>-1683</v>
       </c>
       <c r="O8" t="n">
-        <v>-5</v>
+        <v>-288</v>
       </c>
       <c r="P8" t="n">
-        <v>-2</v>
+        <v>119</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5</v>
+        <v>62</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-2583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
+          <t>Other Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-263</v>
+        <v>186</v>
       </c>
       <c r="C9" t="n">
-        <v>-286</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-303</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-319</v>
+        <v>191</v>
       </c>
       <c r="F9" t="n">
-        <v>-332</v>
+        <v>-5</v>
       </c>
       <c r="G9" t="n">
-        <v>-241</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-170</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-143</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-207</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-71</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-109</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-124</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-135</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-29</v>
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Income (Loss) Attributable to Parent, before Tax</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1212</v>
+        <v>-312</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-263</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-286</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-303</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-319</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-332</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-241</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-143</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-207</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-135</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Provision for Income Taxes</t>
+          <t>Income (Loss) Attributable to Parent, before Tax</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-183</v>
+        <v>427</v>
       </c>
       <c r="C11" t="n">
-        <v>-204</v>
+        <v>1212</v>
       </c>
       <c r="D11" t="n">
-        <v>-76</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-555</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-169</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-123</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-178</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-236</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>485</v>
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1029</v>
+        <v>-122</v>
       </c>
       <c r="C12" t="n">
-        <v>652</v>
+        <v>-183</v>
       </c>
       <c r="D12" t="n">
-        <v>327</v>
+        <v>-204</v>
       </c>
       <c r="E12" t="n">
-        <v>-268</v>
+        <v>-76</v>
       </c>
       <c r="F12" t="n">
-        <v>1888</v>
+        <v>176</v>
       </c>
       <c r="G12" t="n">
-        <v>365</v>
+        <v>-555</v>
       </c>
       <c r="H12" t="n">
-        <v>-35</v>
+        <v>-159</v>
       </c>
       <c r="I12" t="n">
-        <v>502</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>476</v>
+        <v>-169</v>
       </c>
       <c r="K12" t="n">
-        <v>699</v>
+        <v>-123</v>
       </c>
       <c r="L12" t="n">
-        <v>668</v>
+        <v>-178</v>
       </c>
       <c r="M12" t="n">
-        <v>-1365</v>
+        <v>-236</v>
       </c>
       <c r="N12" t="n">
-        <v>-285</v>
+        <v>407</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>-31</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2043</v>
+        <v>115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Preferred Stock Dividends, Income Statement Impact</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-49</v>
+        <v>305</v>
       </c>
       <c r="C13" t="n">
-        <v>-48</v>
+        <v>1029</v>
       </c>
       <c r="D13" t="n">
-        <v>-47</v>
+        <v>652</v>
       </c>
       <c r="E13" t="n">
-        <v>-49</v>
+        <v>327</v>
       </c>
       <c r="F13" t="n">
-        <v>-48</v>
+        <v>-268</v>
       </c>
       <c r="G13" t="n">
-        <v>-47</v>
+        <v>1888</v>
       </c>
       <c r="H13" t="n">
-        <v>-49</v>
+        <v>365</v>
       </c>
       <c r="I13" t="n">
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="J13" t="n">
-        <v>-37</v>
+        <v>502</v>
       </c>
       <c r="K13" t="n">
-        <v>-38</v>
+        <v>476</v>
       </c>
       <c r="L13" t="n">
-        <v>-37</v>
+        <v>699</v>
       </c>
       <c r="M13" t="n">
-        <v>-37</v>
+        <v>668</v>
       </c>
       <c r="N13" t="n">
-        <v>-38</v>
+        <v>-1365</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-285</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2043</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Net Income (Loss) Available to Common Stockholders, Basic</t>
+          <t>Preferred Stock Dividends, Income Statement Impact</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>980</v>
+        <v>-47</v>
       </c>
       <c r="C14" t="n">
-        <v>604</v>
+        <v>-49</v>
       </c>
       <c r="D14" t="n">
-        <v>280</v>
+        <v>-48</v>
       </c>
       <c r="E14" t="n">
-        <v>-317</v>
+        <v>-47</v>
       </c>
       <c r="F14" t="n">
-        <v>1840</v>
+        <v>-49</v>
       </c>
       <c r="G14" t="n">
-        <v>318</v>
+        <v>-48</v>
       </c>
       <c r="H14" t="n">
-        <v>-84</v>
+        <v>-47</v>
       </c>
       <c r="I14" t="n">
-        <v>465</v>
+        <v>-49</v>
       </c>
       <c r="J14" t="n">
-        <v>439</v>
+        <v>-37</v>
       </c>
       <c r="K14" t="n">
-        <v>661</v>
+        <v>-37</v>
       </c>
       <c r="L14" t="n">
-        <v>631</v>
+        <v>-38</v>
       </c>
       <c r="M14" t="n">
-        <v>-1402</v>
+        <v>-37</v>
       </c>
       <c r="N14" t="n">
-        <v>-323</v>
+        <v>-37</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Basic</t>
+          <t>Net Income (Loss) Available to Common Stockholders, Basic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>337824</v>
+        <v>258</v>
       </c>
       <c r="C15" t="n">
-        <v>338749</v>
+        <v>980</v>
       </c>
       <c r="D15" t="n">
-        <v>339402</v>
+        <v>604</v>
       </c>
       <c r="E15" t="n">
-        <v>339800</v>
+        <v>280</v>
       </c>
       <c r="F15" t="n">
-        <v>342970</v>
+        <v>-317</v>
       </c>
       <c r="G15" t="n">
-        <v>347046</v>
+        <v>1840</v>
       </c>
       <c r="H15" t="n">
-        <v>348966</v>
+        <v>318</v>
       </c>
       <c r="I15" t="n">
-        <v>366570</v>
+        <v>-84</v>
       </c>
       <c r="J15" t="n">
-        <v>372956</v>
+        <v>465</v>
       </c>
       <c r="K15" t="n">
-        <v>383631</v>
+        <v>439</v>
       </c>
       <c r="L15" t="n">
-        <v>413763</v>
+        <v>661</v>
       </c>
       <c r="M15" t="n">
-        <v>429193</v>
+        <v>631</v>
       </c>
       <c r="N15" t="n">
-        <v>451603</v>
+        <v>-1402</v>
       </c>
       <c r="O15" t="n">
-        <v>482517</v>
+        <v>-323</v>
       </c>
       <c r="P15" t="n">
-        <v>486023</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>484699</v>
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Diluted</t>
+          <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>341857</v>
+        <v>336847</v>
       </c>
       <c r="C16" t="n">
-        <v>345035</v>
+        <v>337824</v>
       </c>
       <c r="D16" t="n">
-        <v>345505</v>
+        <v>338749</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>339402</v>
       </c>
       <c r="F16" t="n">
-        <v>350204</v>
+        <v>339800</v>
       </c>
       <c r="G16" t="n">
-        <v>354327</v>
+        <v>342970</v>
       </c>
       <c r="H16" t="n">
+        <v>347046</v>
+      </c>
+      <c r="I16" t="n">
         <v>348966</v>
       </c>
-      <c r="I16" t="n">
-        <v>372149</v>
-      </c>
       <c r="J16" t="n">
-        <v>376794</v>
+        <v>366570</v>
       </c>
       <c r="K16" t="n">
-        <v>387553</v>
+        <v>372956</v>
       </c>
       <c r="L16" t="n">
-        <v>417483</v>
+        <v>383631</v>
       </c>
       <c r="M16" t="n">
+        <v>413763</v>
+      </c>
+      <c r="N16" t="n">
         <v>429193</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
-        <v>484495</v>
+        <v>451603</v>
       </c>
       <c r="P16" t="n">
-        <v>487366</v>
+        <v>482517</v>
       </c>
       <c r="Q16" t="n">
+        <v>486023</v>
+      </c>
+      <c r="R16" t="n">
         <v>484699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Basic</t>
+          <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>339231</v>
       </c>
       <c r="C17" t="n">
-        <v>1.78</v>
+        <v>341857</v>
       </c>
       <c r="D17" t="n">
-        <v>0.82</v>
+        <v>345035</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.93</v>
+        <v>345505</v>
       </c>
       <c r="F17" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.92</v>
+        <v>350204</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.24</v>
+        <v>354327</v>
       </c>
       <c r="I17" t="n">
-        <v>1.27</v>
+        <v>348966</v>
       </c>
       <c r="J17" t="n">
-        <v>1.18</v>
+        <v>372149</v>
       </c>
       <c r="K17" t="n">
-        <v>1.72</v>
+        <v>376794</v>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>387553</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.27</v>
+        <v>417483</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.72</v>
+        <v>429193</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.07000000000000001</v>
+        <v>484495</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.21</v>
+        <v>487366</v>
+      </c>
+      <c r="R17" t="n">
+        <v>484699</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Diluted</t>
+          <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.87</v>
+        <v>0.77</v>
       </c>
       <c r="C18" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="F18" t="n">
-        <v>5.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9</v>
+        <v>5.36</v>
       </c>
       <c r="H18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I18" t="n">
         <v>-0.24</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="J18" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="K18" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-3.27</v>
       </c>
       <c r="O18" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="P18" t="n">
         <v>0.01</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-4.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Impairment of Long-Lived Assets Held-for-use</t>
+          <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="C19" t="n">
-        <v>-5</v>
+        <v>2.87</v>
       </c>
       <c r="D19" t="n">
-        <v>-68</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-49</v>
+        <v>1.17</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -4449,23 +4781,26 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-38</v>
+        <v>0.01</v>
       </c>
       <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Other Nonoperating Income</t>
+          <t>Other Nonoperating Expense</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>-24</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4474,46 +4809,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>62</v>
+        <v>-3</v>
       </c>
       <c r="H20" t="n">
-        <v>91</v>
+        <v>-3</v>
       </c>
       <c r="I20" t="n">
-        <v>32</v>
+        <v>-4</v>
       </c>
       <c r="J20" t="n">
-        <v>124</v>
+        <v>-3</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
       <c r="M20" t="n">
-        <v>71</v>
+        <v>-5</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="P20" t="n">
-        <v>36</v>
+        <v>-5</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>-2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Impacts Of Tax Receivable Agreement</t>
+          <t>Other Nonoperating Income</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -4523,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4532,153 +4870,162 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H21" t="n">
-        <v>-5</v>
+        <v>62</v>
       </c>
       <c r="I21" t="n">
-        <v>-49</v>
+        <v>91</v>
       </c>
       <c r="J21" t="n">
-        <v>-14</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-65</v>
+        <v>124</v>
       </c>
       <c r="L21" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="M21" t="n">
-        <v>-34</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>-81</v>
+        <v>71</v>
       </c>
       <c r="O21" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>-41</v>
+        <v>16</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="R21" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Income Before Provision for Income Taxes</t>
+          <t>Impacts Of Tax Receivable Agreement</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-444</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2392</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>671</v>
+        <v>-5</v>
       </c>
       <c r="J22" t="n">
-        <v>599</v>
+        <v>-49</v>
       </c>
       <c r="K22" t="n">
-        <v>876</v>
+        <v>-14</v>
       </c>
       <c r="L22" t="n">
-        <v>914</v>
+        <v>-65</v>
       </c>
       <c r="M22" t="n">
-        <v>-1764</v>
+        <v>86</v>
       </c>
       <c r="N22" t="n">
-        <v>-375</v>
+        <v>-34</v>
       </c>
       <c r="O22" t="n">
-        <v>41</v>
+        <v>-81</v>
       </c>
       <c r="P22" t="n">
-        <v>-80</v>
+        <v>35</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2525</v>
+        <v>-41</v>
+      </c>
+      <c r="R22" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
+          <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>327</v>
+        <v>856</v>
       </c>
       <c r="E23" t="n">
-        <v>-268</v>
+        <v>403</v>
       </c>
       <c r="F23" t="n">
-        <v>1837</v>
+        <v>-444</v>
       </c>
       <c r="G23" t="n">
-        <v>467</v>
+        <v>2392</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>626</v>
       </c>
       <c r="I23" t="n">
-        <v>502</v>
+        <v>-2</v>
       </c>
       <c r="J23" t="n">
-        <v>476</v>
+        <v>671</v>
       </c>
       <c r="K23" t="n">
-        <v>698</v>
+        <v>599</v>
       </c>
       <c r="L23" t="n">
-        <v>678</v>
+        <v>876</v>
       </c>
       <c r="M23" t="n">
-        <v>-1357</v>
+        <v>914</v>
       </c>
       <c r="N23" t="n">
-        <v>-284</v>
+        <v>-1764</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>-375</v>
       </c>
       <c r="P23" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2040</v>
+        <v>-80</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-2525</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Net Income (Loss) Attributable to Noncontrolling Interest</t>
+          <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4688,52 +5035,55 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>-268</v>
       </c>
       <c r="G24" t="n">
-        <v>-102</v>
+        <v>1837</v>
       </c>
       <c r="H24" t="n">
-        <v>-53</v>
+        <v>467</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>476</v>
       </c>
       <c r="L24" t="n">
-        <v>-10</v>
+        <v>698</v>
       </c>
       <c r="M24" t="n">
-        <v>-8</v>
+        <v>678</v>
       </c>
       <c r="N24" t="n">
-        <v>-1</v>
+        <v>-1357</v>
       </c>
       <c r="O24" t="n">
-        <v>-3</v>
+        <v>-284</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3</v>
+        <v>35</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-2040</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Other Nonoperating Income (Expense)</t>
+          <t>Net Income (Loss) Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4743,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-102</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -4767,22 +5117,25 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
@@ -4837,6 +5190,9 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4851,56 +5207,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -4911,51 +5270,54 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1334</v>
+      </c>
+      <c r="C2" t="n">
         <v>1029</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>711</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>59</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-268</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2322</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>485</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>18</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1676</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1174</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>698</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>-962</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>-1641</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>-284</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>-1994</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>-2004</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>-2040</v>
       </c>
     </row>
@@ -4966,51 +5328,54 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1363</v>
+      </c>
+      <c r="C3" t="n">
         <v>718</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2225</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1534</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>772</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1891</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1177</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>555</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1442</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>941</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>477</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1575</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>542</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1551</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>969</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>511</v>
       </c>
     </row>
@@ -5021,2378 +5386,2507 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>255</v>
+      </c>
+      <c r="C4" t="n">
         <v>159</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>68</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>-128</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-185</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>666</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>115</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-23</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>437</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>290</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>181</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>-298</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>-501</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>-84</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>-587</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>-626</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>-524</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Unrealized Gain Loss On Commodity Related Derivatives</t>
+          <t>Impairment of Long-Lived Assets Held-for-use</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-723</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>551</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
-        <v>567</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>-1725</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-855</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1139</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>-1085</v>
+        <v>49</v>
       </c>
       <c r="L5" t="n">
-        <v>2027</v>
+        <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>2347</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="n">
-        <v>-96</v>
+        <v>38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Unrealized Gain Loss On Interest Rate Swap Derivatives</t>
+          <t>Unrealized Gain Loss On Commodity Related Derivatives</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-16</v>
+        <v>-251</v>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>-723</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>367</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>551</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>567</v>
       </c>
       <c r="G6" t="n">
-        <v>-58</v>
+        <v>-1725</v>
       </c>
       <c r="H6" t="n">
-        <v>-47</v>
+        <v>130</v>
       </c>
       <c r="I6" t="n">
-        <v>-65</v>
+        <v>176</v>
       </c>
       <c r="J6" t="n">
-        <v>-22</v>
+        <v>-855</v>
       </c>
       <c r="K6" t="n">
-        <v>41</v>
+        <v>-1139</v>
       </c>
       <c r="L6" t="n">
-        <v>-261</v>
+        <v>-1085</v>
       </c>
       <c r="M6" t="n">
-        <v>-171</v>
+        <v>2027</v>
       </c>
       <c r="N6" t="n">
-        <v>-126</v>
+        <v>2347</v>
       </c>
       <c r="O6" t="n">
-        <v>-92</v>
+        <v>360</v>
       </c>
       <c r="P6" t="n">
-        <v>-79</v>
+        <v>771</v>
       </c>
       <c r="Q6" t="n">
-        <v>-88</v>
+        <v>182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Unrealized Gain Loss From Nuclear Decommissioning Trusts</t>
+          <t>Unrealized Gain Loss On Interest Rate Swap Derivatives</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>-7</v>
       </c>
       <c r="C7" t="n">
-        <v>-164</v>
+        <v>-16</v>
       </c>
       <c r="D7" t="n">
-        <v>-74</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>-133</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>-55</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>-28</v>
+        <v>-58</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-47</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-261</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-171</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-126</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-79</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Accretion Expense</t>
+          <t>Unrealized Gain Loss From Nuclear Decommissioning Trusts</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>-164</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>-74</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>-133</v>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>-55</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>-28</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Accounts Receivable, Credit Loss Expense (Reversal)</t>
+          <t>Accretion Expense</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I9" t="n">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Share-based Payment Arrangement, Noncash Expense</t>
+          <t>Accounts Receivable, Credit Loss Expense (Reversal)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Other Noncash Income (Expense)</t>
+          <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-12</v>
+        <v>67</v>
       </c>
       <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>82</v>
+      </c>
+      <c r="E11" t="n">
+        <v>46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G11" t="n">
+        <v>76</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>43</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>34</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
         <v>36</v>
       </c>
-      <c r="D11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E11" t="n">
-        <v>57</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-23</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-23</v>
-      </c>
-      <c r="I11" t="n">
-        <v>39</v>
-      </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>66</v>
-      </c>
-      <c r="N11" t="n">
-        <v>32</v>
-      </c>
-      <c r="O11" t="n">
-        <v>79</v>
-      </c>
-      <c r="P11" t="n">
-        <v>56</v>
-      </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) In Margin Deposits, Net</t>
+          <t>Gain On Involuntary Conversion</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>-48</v>
       </c>
       <c r="C12" t="n">
-        <v>-361</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-368</v>
+        <v>-80</v>
       </c>
       <c r="E12" t="n">
-        <v>-217</v>
+        <v>-80</v>
       </c>
       <c r="F12" t="n">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2271</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2014</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1227</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1805</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1893</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-767</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-134</v>
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Interest Payable, Net</t>
+          <t>Other Noncash Income (Expense)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="D13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J13" t="n">
+        <v>39</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>66</v>
+      </c>
+      <c r="O13" t="n">
         <v>32</v>
       </c>
-      <c r="D13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>51</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="P13" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>56</v>
+      </c>
+      <c r="R13" t="n">
         <v>11</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-47</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-47</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-31</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-62</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-55</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accrued Taxes Payable</t>
+          <t>Increase (Decrease) In Margin Deposits, Net</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-110</v>
+        <v>-188</v>
       </c>
       <c r="C14" t="n">
-        <v>-19</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>-56</v>
+        <v>-361</v>
       </c>
       <c r="E14" t="n">
-        <v>-109</v>
+        <v>-368</v>
       </c>
       <c r="F14" t="n">
-        <v>-40</v>
+        <v>-217</v>
       </c>
       <c r="G14" t="n">
-        <v>-58</v>
+        <v>855</v>
       </c>
       <c r="H14" t="n">
-        <v>-111</v>
+        <v>433</v>
       </c>
       <c r="I14" t="n">
-        <v>-38</v>
+        <v>128</v>
       </c>
       <c r="J14" t="n">
-        <v>-52</v>
+        <v>2271</v>
       </c>
       <c r="K14" t="n">
-        <v>-91</v>
+        <v>2014</v>
       </c>
       <c r="L14" t="n">
-        <v>-46</v>
+        <v>1227</v>
       </c>
       <c r="M14" t="n">
-        <v>-62</v>
+        <v>-1805</v>
       </c>
       <c r="N14" t="n">
-        <v>-98</v>
+        <v>-1893</v>
       </c>
       <c r="O14" t="n">
-        <v>-63</v>
+        <v>210</v>
       </c>
       <c r="P14" t="n">
-        <v>-75</v>
+        <v>-767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-79</v>
+        <v>-240</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Employee Related Liabilities</t>
+          <t>Increase (Decrease) in Interest Payable, Net</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-135</v>
+        <v>61</v>
       </c>
       <c r="C15" t="n">
-        <v>-106</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>-145</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-177</v>
+        <v>-5</v>
       </c>
       <c r="F15" t="n">
-        <v>-78</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>-140</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>-169</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>-23</v>
+        <v>-3</v>
       </c>
       <c r="J15" t="n">
-        <v>-57</v>
+        <v>-47</v>
       </c>
       <c r="K15" t="n">
-        <v>-79</v>
+        <v>-4</v>
       </c>
       <c r="L15" t="n">
-        <v>-17</v>
+        <v>-47</v>
       </c>
       <c r="M15" t="n">
-        <v>-38</v>
+        <v>-31</v>
       </c>
       <c r="N15" t="n">
-        <v>-59</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
-        <v>-86</v>
+        <v>-62</v>
       </c>
       <c r="P15" t="n">
-        <v>-107</v>
+        <v>-55</v>
       </c>
       <c r="Q15" t="n">
-        <v>-128</v>
+        <v>8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
+          <t>Increase (Decrease) in Accrued Taxes Payable</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-111</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-38</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-52</v>
+      </c>
+      <c r="L16" t="n">
         <v>-91</v>
       </c>
-      <c r="C16" t="n">
-        <v>-562</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-471</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-54</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-863</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-674</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-232</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-567</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-320</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
+        <v>-46</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-62</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-98</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-63</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-75</v>
       </c>
-      <c r="L16" t="n">
-        <v>-873</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-607</v>
-      </c>
-      <c r="N16" t="n">
-        <v>56</v>
-      </c>
-      <c r="O16" t="n">
-        <v>680</v>
-      </c>
-      <c r="P16" t="n">
-        <v>773</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>999</v>
+      <c r="R16" t="n">
+        <v>-79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Operating Activities</t>
+          <t>Increase (Decrease) in Employee Related Liabilities</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1199</v>
+        <v>-99</v>
       </c>
       <c r="C17" t="n">
-        <v>2638</v>
+        <v>-135</v>
       </c>
       <c r="D17" t="n">
-        <v>1171</v>
+        <v>-106</v>
       </c>
       <c r="E17" t="n">
-        <v>599</v>
+        <v>-145</v>
       </c>
       <c r="F17" t="n">
-        <v>3210</v>
+        <v>-177</v>
       </c>
       <c r="G17" t="n">
-        <v>1508</v>
+        <v>-78</v>
       </c>
       <c r="H17" t="n">
-        <v>312</v>
+        <v>-140</v>
       </c>
       <c r="I17" t="n">
-        <v>4572</v>
+        <v>-169</v>
       </c>
       <c r="J17" t="n">
-        <v>3012</v>
+        <v>-23</v>
       </c>
       <c r="K17" t="n">
-        <v>1435</v>
+        <v>-57</v>
       </c>
       <c r="L17" t="n">
-        <v>92</v>
+        <v>-79</v>
       </c>
       <c r="M17" t="n">
-        <v>-723</v>
+        <v>-17</v>
       </c>
       <c r="N17" t="n">
-        <v>591</v>
+        <v>-38</v>
       </c>
       <c r="O17" t="n">
-        <v>-493</v>
+        <v>-59</v>
       </c>
       <c r="P17" t="n">
-        <v>-1057</v>
+        <v>-86</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1653</v>
+        <v>-107</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Property, Plant, and Equipment</t>
+          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-883</v>
+        <v>-336</v>
       </c>
       <c r="C18" t="n">
-        <v>-1916</v>
+        <v>-91</v>
       </c>
       <c r="D18" t="n">
-        <v>-1458</v>
+        <v>-562</v>
       </c>
       <c r="E18" t="n">
-        <v>-768</v>
+        <v>-471</v>
       </c>
       <c r="F18" t="n">
-        <v>-1648</v>
+        <v>-54</v>
       </c>
       <c r="G18" t="n">
-        <v>-963</v>
+        <v>-863</v>
       </c>
       <c r="H18" t="n">
-        <v>-465</v>
+        <v>-674</v>
       </c>
       <c r="I18" t="n">
-        <v>-1262</v>
+        <v>-232</v>
       </c>
       <c r="J18" t="n">
-        <v>-926</v>
+        <v>-567</v>
       </c>
       <c r="K18" t="n">
-        <v>-484</v>
+        <v>-320</v>
       </c>
       <c r="L18" t="n">
-        <v>-909</v>
+        <v>-75</v>
       </c>
       <c r="M18" t="n">
-        <v>-613</v>
+        <v>-873</v>
       </c>
       <c r="N18" t="n">
-        <v>-373</v>
+        <v>-607</v>
       </c>
       <c r="O18" t="n">
-        <v>-790</v>
+        <v>56</v>
       </c>
       <c r="P18" t="n">
-        <v>-546</v>
+        <v>680</v>
       </c>
       <c r="Q18" t="n">
-        <v>-192</v>
+        <v>773</v>
+      </c>
+      <c r="R18" t="n">
+        <v>999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
+          <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>2222</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2638</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="F19" t="n">
-        <v>-3065</v>
+        <v>599</v>
       </c>
       <c r="G19" t="n">
-        <v>-3065</v>
+        <v>3210</v>
       </c>
       <c r="H19" t="n">
-        <v>-3070</v>
+        <v>1508</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4572</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3012</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-723</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-493</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1057</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1653</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Decommissioning Trust Fund Assets</t>
+          <t>Payments to Acquire Property, Plant, and Equipment</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1821</v>
+        <v>-1572</v>
       </c>
       <c r="C20" t="n">
-        <v>4120</v>
+        <v>-883</v>
       </c>
       <c r="D20" t="n">
-        <v>3024</v>
+        <v>-1916</v>
       </c>
       <c r="E20" t="n">
-        <v>2107</v>
+        <v>-1458</v>
       </c>
       <c r="F20" t="n">
-        <v>1573</v>
+        <v>-768</v>
       </c>
       <c r="G20" t="n">
-        <v>777</v>
+        <v>-1648</v>
       </c>
       <c r="H20" t="n">
-        <v>214</v>
+        <v>-963</v>
       </c>
       <c r="I20" t="n">
-        <v>478</v>
+        <v>-465</v>
       </c>
       <c r="J20" t="n">
-        <v>251</v>
+        <v>-1262</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>-926</v>
       </c>
       <c r="L20" t="n">
-        <v>428</v>
+        <v>-484</v>
       </c>
       <c r="M20" t="n">
-        <v>334</v>
+        <v>-909</v>
       </c>
       <c r="N20" t="n">
-        <v>98</v>
+        <v>-613</v>
       </c>
       <c r="O20" t="n">
-        <v>366</v>
+        <v>-373</v>
       </c>
       <c r="P20" t="n">
-        <v>267</v>
+        <v>-790</v>
       </c>
       <c r="Q20" t="n">
-        <v>133</v>
+        <v>-546</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-192</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Investments to be Held in Decommissioning Trust Fund</t>
+          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1822</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>-4138</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-3035</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-2112</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1590</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-788</v>
+        <v>-3065</v>
       </c>
       <c r="H21" t="n">
-        <v>-220</v>
+        <v>-3065</v>
       </c>
       <c r="I21" t="n">
-        <v>-495</v>
+        <v>-3070</v>
       </c>
       <c r="J21" t="n">
-        <v>-262</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-125</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-446</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-345</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-382</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-277</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-138</v>
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale of Intangible Assets</t>
+          <t>Proceeds from Decommissioning Trust Fund Assets</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>121</v>
+        <v>3036</v>
       </c>
       <c r="C22" t="n">
-        <v>57</v>
+        <v>1821</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>4120</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>3024</v>
       </c>
       <c r="F22" t="n">
-        <v>147</v>
+        <v>2107</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>1573</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>777</v>
       </c>
       <c r="I22" t="n">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="J22" t="n">
-        <v>47</v>
+        <v>478</v>
       </c>
       <c r="K22" t="n">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
-        <v>358</v>
+        <v>119</v>
       </c>
       <c r="M22" t="n">
-        <v>266</v>
+        <v>428</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>334</v>
       </c>
       <c r="O22" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="P22" t="n">
-        <v>64</v>
+        <v>366</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>267</v>
+      </c>
+      <c r="R22" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Intangible Assets</t>
+          <t>Payments to Acquire Investments to be Held in Decommissioning Trust Fund</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-160</v>
+        <v>-3037</v>
       </c>
       <c r="C23" t="n">
-        <v>-511</v>
+        <v>-1822</v>
       </c>
       <c r="D23" t="n">
-        <v>-392</v>
+        <v>-4138</v>
       </c>
       <c r="E23" t="n">
-        <v>-307</v>
+        <v>-3035</v>
       </c>
       <c r="F23" t="n">
-        <v>-511</v>
+        <v>-2112</v>
       </c>
       <c r="G23" t="n">
-        <v>-359</v>
+        <v>-1590</v>
       </c>
       <c r="H23" t="n">
-        <v>-131</v>
+        <v>-788</v>
       </c>
       <c r="I23" t="n">
+        <v>-220</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-495</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-262</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-125</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-446</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-345</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-103</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-382</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-277</v>
       </c>
-      <c r="J23" t="n">
-        <v>-190</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-61</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-343</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-258</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-116</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-247</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-173</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-28</v>
+      <c r="R23" t="n">
+        <v>-138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Insurance Settlement, Investing Activities</t>
+          <t>Proceeds from Sale of Intangible Assets</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="C24" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
       <c r="D24" t="n">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="O24" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="R24" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale of Other Productive Assets</t>
+          <t>Payments to Acquire Intangible Assets</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>-201</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>-160</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-511</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-392</v>
       </c>
       <c r="F25" t="n">
-        <v>137</v>
+        <v>-307</v>
       </c>
       <c r="G25" t="n">
-        <v>129</v>
+        <v>-511</v>
       </c>
       <c r="H25" t="n">
-        <v>127</v>
+        <v>-359</v>
       </c>
       <c r="I25" t="n">
-        <v>111</v>
+        <v>-131</v>
       </c>
       <c r="J25" t="n">
-        <v>110</v>
+        <v>-277</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>-190</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>-61</v>
       </c>
       <c r="M25" t="n">
-        <v>14</v>
+        <v>-343</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-258</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>-116</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-173</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Other Investing Activities</t>
+          <t>Proceeds from Insurance Settlement, Investing Activities</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="D26" t="n">
-        <v>-8</v>
+        <v>198</v>
       </c>
       <c r="E26" t="n">
-        <v>-2</v>
+        <v>173</v>
       </c>
       <c r="F26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-6</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="L26" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="R26" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>Proceeds from Sale of Other Productive Assets</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-638</v>
+        <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>-2162</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>-1671</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>-1061</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-4959</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-4197</v>
+        <v>137</v>
       </c>
       <c r="H27" t="n">
-        <v>-3528</v>
+        <v>129</v>
       </c>
       <c r="I27" t="n">
-        <v>-1382</v>
+        <v>127</v>
       </c>
       <c r="J27" t="n">
-        <v>-967</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
-        <v>-513</v>
+        <v>110</v>
       </c>
       <c r="L27" t="n">
-        <v>-886</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>-609</v>
+        <v>21</v>
       </c>
       <c r="N27" t="n">
-        <v>-480</v>
+        <v>14</v>
       </c>
       <c r="O27" t="n">
-        <v>-843</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-575</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>-129</v>
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Debt</t>
+          <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2250</v>
+        <v>77</v>
       </c>
       <c r="C28" t="n">
-        <v>424</v>
+        <v>65</v>
       </c>
       <c r="D28" t="n">
-        <v>209</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="F28" t="n">
-        <v>2200</v>
+        <v>-2</v>
       </c>
       <c r="G28" t="n">
-        <v>2200</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>700</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L28" t="n">
-        <v>1498</v>
+        <v>-2</v>
       </c>
       <c r="M28" t="n">
-        <v>1498</v>
+        <v>-10</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="O28" t="n">
-        <v>1250</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>1250</v>
+        <v>27</v>
       </c>
       <c r="Q28" t="n">
-        <v>1000</v>
+        <v>27</v>
+      </c>
+      <c r="R28" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Long-term Debt</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-115</v>
+        <v>-1279</v>
       </c>
       <c r="C29" t="n">
-        <v>-764</v>
+        <v>-638</v>
       </c>
       <c r="D29" t="n">
-        <v>-757</v>
+        <v>-2162</v>
       </c>
       <c r="E29" t="n">
-        <v>-6</v>
+        <v>-1671</v>
       </c>
       <c r="F29" t="n">
-        <v>-2269</v>
+        <v>-1061</v>
       </c>
       <c r="G29" t="n">
-        <v>-1106</v>
+        <v>-4959</v>
       </c>
       <c r="H29" t="n">
-        <v>-756</v>
+        <v>-4197</v>
       </c>
       <c r="I29" t="n">
-        <v>-21</v>
+        <v>-3528</v>
       </c>
       <c r="J29" t="n">
-        <v>-14</v>
+        <v>-1382</v>
       </c>
       <c r="K29" t="n">
-        <v>-7</v>
+        <v>-967</v>
       </c>
       <c r="L29" t="n">
-        <v>-232</v>
+        <v>-513</v>
       </c>
       <c r="M29" t="n">
-        <v>-223</v>
+        <v>-886</v>
       </c>
       <c r="N29" t="n">
-        <v>-132</v>
+        <v>-609</v>
       </c>
       <c r="O29" t="n">
-        <v>-234</v>
+        <v>-480</v>
       </c>
       <c r="P29" t="n">
-        <v>-101</v>
+        <v>-843</v>
       </c>
       <c r="Q29" t="n">
-        <v>-36</v>
+        <v>-575</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Proceeds From Repayments Of Accounts Receivable Financing</t>
+          <t>Proceeds from Issuance of Debt</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-475</v>
+        <v>6422</v>
       </c>
       <c r="C30" t="n">
-        <v>475</v>
+        <v>2250</v>
       </c>
       <c r="D30" t="n">
-        <v>375</v>
+        <v>424</v>
       </c>
       <c r="E30" t="n">
-        <v>332</v>
+        <v>209</v>
       </c>
       <c r="F30" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>750</v>
+        <v>2200</v>
       </c>
       <c r="H30" t="n">
-        <v>875</v>
+        <v>2200</v>
       </c>
       <c r="I30" t="n">
-        <v>-425</v>
+        <v>700</v>
       </c>
       <c r="J30" t="n">
-        <v>-425</v>
+        <v>1750</v>
       </c>
       <c r="K30" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>725</v>
+        <v>1498</v>
       </c>
       <c r="N30" t="n">
-        <v>500</v>
+        <v>1498</v>
       </c>
       <c r="O30" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>361</v>
+        <v>1250</v>
       </c>
       <c r="Q30" t="n">
-        <v>425</v>
+        <v>1250</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Lines of Credit</t>
+          <t>Repayments of Long-term Debt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>-3859</v>
       </c>
       <c r="C31" t="n">
-        <v>150</v>
+        <v>-115</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-764</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-757</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>-6</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-2269</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-1106</v>
       </c>
       <c r="I31" t="n">
-        <v>100</v>
+        <v>-756</v>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>-21</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>-14</v>
       </c>
       <c r="L31" t="n">
-        <v>1500</v>
+        <v>-7</v>
       </c>
       <c r="M31" t="n">
-        <v>1500</v>
+        <v>-232</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>-223</v>
       </c>
       <c r="O31" t="n">
-        <v>1300</v>
+        <v>-132</v>
       </c>
       <c r="P31" t="n">
-        <v>1300</v>
+        <v>-234</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>-101</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Lines of Credit</t>
+          <t>Proceeds From Repayments Of Accounts Receivable Financing</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-530</v>
+        <v>-925</v>
       </c>
       <c r="C32" t="n">
-        <v>-150</v>
+        <v>-475</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="F32" t="n">
-        <v>-50</v>
+        <v>332</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I32" t="n">
-        <v>-350</v>
+        <v>875</v>
       </c>
       <c r="J32" t="n">
-        <v>-350</v>
+        <v>-425</v>
       </c>
       <c r="K32" t="n">
-        <v>-350</v>
+        <v>-425</v>
       </c>
       <c r="L32" t="n">
-        <v>-1500</v>
+        <v>175</v>
       </c>
       <c r="M32" t="n">
-        <v>-1250</v>
+        <v>625</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="O32" t="n">
-        <v>-1300</v>
+        <v>500</v>
       </c>
       <c r="P32" t="n">
-        <v>-1300</v>
+        <v>175</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>361</v>
+      </c>
+      <c r="R32" t="n">
+        <v>425</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Short-term Debt</t>
+          <t>Proceeds from Lines of Credit</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1420</v>
+        <v>400</v>
       </c>
       <c r="C33" t="n">
-        <v>-987</v>
+        <v>150</v>
       </c>
       <c r="D33" t="n">
-        <v>-126</v>
+        <v>150</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-1802</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-500</v>
+        <v>50</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>-2750</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>-1700</v>
+        <v>1500</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="O33" t="n">
-        <v>-1250</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1000</v>
+        <v>1300</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Payments of Financing Costs</t>
+          <t>Repayments of Lines of Credit</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-26</v>
+        <v>-780</v>
       </c>
       <c r="C34" t="n">
-        <v>-2</v>
+        <v>-530</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-32</v>
+        <v>-50</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-6</v>
+        <v>-350</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="L34" t="n">
-        <v>-29</v>
+        <v>-350</v>
       </c>
       <c r="M34" t="n">
-        <v>-21</v>
+        <v>-1500</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>-1250</v>
       </c>
       <c r="O34" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-13</v>
+        <v>-1300</v>
       </c>
       <c r="Q34" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="R34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Proceeds from Short-term Debt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-372</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-776</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-589</v>
+        <v>987</v>
       </c>
       <c r="E35" t="n">
-        <v>-337</v>
+        <v>987</v>
       </c>
       <c r="F35" t="n">
-        <v>-1021</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-622</v>
+        <v>1802</v>
       </c>
       <c r="H35" t="n">
-        <v>-291</v>
+        <v>500</v>
       </c>
       <c r="I35" t="n">
-        <v>-866</v>
+        <v>500</v>
       </c>
       <c r="J35" t="n">
-        <v>-552</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>-301</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>-1590</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1194</v>
+        <v>2750</v>
       </c>
       <c r="N35" t="n">
-        <v>-710</v>
+        <v>2750</v>
       </c>
       <c r="O35" t="n">
-        <v>-175</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-175</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>-175</v>
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Payments of Dividends</t>
+          <t>Repayments of Short-term Debt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-77</v>
+        <v>-1420</v>
       </c>
       <c r="C36" t="n">
-        <v>-229</v>
+        <v>-1420</v>
       </c>
       <c r="D36" t="n">
-        <v>-152</v>
+        <v>-987</v>
       </c>
       <c r="E36" t="n">
-        <v>-83</v>
+        <v>-126</v>
       </c>
       <c r="F36" t="n">
-        <v>-230</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-150</v>
+        <v>-1802</v>
       </c>
       <c r="H36" t="n">
-        <v>-77</v>
+        <v>-500</v>
       </c>
       <c r="I36" t="n">
-        <v>-228</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-153</v>
+        <v>-400</v>
       </c>
       <c r="K36" t="n">
-        <v>-77</v>
+        <v>-400</v>
       </c>
       <c r="L36" t="n">
-        <v>-227</v>
+        <v>-400</v>
       </c>
       <c r="M36" t="n">
-        <v>-152</v>
+        <v>-2750</v>
       </c>
       <c r="N36" t="n">
-        <v>-77</v>
+        <v>-1700</v>
       </c>
       <c r="O36" t="n">
-        <v>-219</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-147</v>
+        <v>-1250</v>
       </c>
       <c r="Q36" t="n">
-        <v>-74</v>
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-1000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Payments of Ordinary Dividends, Preferred Stock and Preference Stock</t>
+          <t>Payments of Financing Costs</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>-72</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-26</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-29</v>
+      </c>
+      <c r="N37" t="n">
         <v>-21</v>
       </c>
-      <c r="C37" t="n">
-        <v>-117</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-96</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-21</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-98</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-75</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-75</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-76</v>
-      </c>
-      <c r="M37" t="n">
-        <v>-76</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="Q37" t="n">
+        <v>-13</v>
+      </c>
+      <c r="R37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-69</v>
+        <v>-709</v>
       </c>
       <c r="C38" t="n">
-        <v>-51</v>
+        <v>-372</v>
       </c>
       <c r="D38" t="n">
-        <v>-50</v>
+        <v>-776</v>
       </c>
       <c r="E38" t="n">
-        <v>-50</v>
+        <v>-589</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-337</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1021</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-622</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>-291</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-866</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>-552</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>-301</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>-1590</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>-1194</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>-710</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>-175</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>-175</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-175</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1</v>
+        <v>-154</v>
       </c>
       <c r="C39" t="n">
-        <v>21</v>
+        <v>-77</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>-229</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>-152</v>
       </c>
       <c r="F39" t="n">
-        <v>-13</v>
+        <v>-83</v>
       </c>
       <c r="G39" t="n">
-        <v>-17</v>
+        <v>-230</v>
       </c>
       <c r="H39" t="n">
-        <v>-36</v>
+        <v>-150</v>
       </c>
       <c r="I39" t="n">
-        <v>54</v>
+        <v>-77</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>-228</v>
       </c>
       <c r="K39" t="n">
-        <v>-14</v>
+        <v>-153</v>
       </c>
       <c r="L39" t="n">
-        <v>34</v>
+        <v>-77</v>
       </c>
       <c r="M39" t="n">
-        <v>23</v>
+        <v>-227</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>-152</v>
       </c>
       <c r="O39" t="n">
-        <v>-5</v>
+        <v>-77</v>
       </c>
       <c r="P39" t="n">
-        <v>-4</v>
+        <v>-219</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1</v>
+        <v>-147</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Payments of Ordinary Dividends, Preferred Stock and Preference Stock</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-706</v>
+        <v>-96</v>
       </c>
       <c r="C40" t="n">
-        <v>-1060</v>
+        <v>-21</v>
       </c>
       <c r="D40" t="n">
-        <v>-227</v>
+        <v>-117</v>
       </c>
       <c r="E40" t="n">
-        <v>-164</v>
+        <v>-96</v>
       </c>
       <c r="F40" t="n">
-        <v>-850</v>
+        <v>-21</v>
       </c>
       <c r="G40" t="n">
-        <v>811</v>
+        <v>-98</v>
       </c>
       <c r="H40" t="n">
-        <v>793</v>
+        <v>-75</v>
       </c>
       <c r="I40" t="n">
-        <v>-490</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1872</v>
+        <v>-75</v>
       </c>
       <c r="K40" t="n">
-        <v>-874</v>
+        <v>-75</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1880</v>
+        <v>-76</v>
       </c>
       <c r="N40" t="n">
-        <v>-413</v>
+        <v>-76</v>
       </c>
       <c r="O40" t="n">
-        <v>1279</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1671</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1939</v>
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-145</v>
+        <v>-69</v>
       </c>
       <c r="C41" t="n">
-        <v>-584</v>
+        <v>-69</v>
       </c>
       <c r="D41" t="n">
-        <v>-727</v>
+        <v>-51</v>
       </c>
       <c r="E41" t="n">
-        <v>-626</v>
+        <v>-50</v>
       </c>
       <c r="F41" t="n">
-        <v>-2599</v>
+        <v>-50</v>
       </c>
       <c r="G41" t="n">
-        <v>-1878</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2423</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>-791</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>548</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-302</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>-57</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>157</v>
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Redeemable Noncontrolling Interest Principal Payment</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>822</v>
+        <v>-19</v>
       </c>
       <c r="C42" t="n">
-        <v>1222</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1222</v>
+        <v>-41</v>
       </c>
       <c r="E42" t="n">
-        <v>1222</v>
+        <v>-41</v>
       </c>
       <c r="F42" t="n">
-        <v>3539</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3539</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3539</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>444</v>
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>202</v>
+        <v>-3</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Interest Costs Capitalized</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-42</v>
+        <v>-1284</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>-706</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-1060</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-227</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-164</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-850</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-490</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-1872</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-874</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>-413</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1279</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1671</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1939</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Interest Paid, Including Capitalized Interest, Operating and Investing Activities</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>160</v>
+        <v>-341</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>-145</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-584</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-727</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-626</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-2599</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-1878</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-2423</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>-791</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-302</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="R45" t="n">
+        <v>157</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Impairment of Long-Lived Assets Held-for-use</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="C46" t="n">
-        <v>73</v>
+        <v>822</v>
       </c>
       <c r="D46" t="n">
-        <v>68</v>
+        <v>1222</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3539</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3539</v>
       </c>
       <c r="I46" t="n">
-        <v>49</v>
+        <v>3539</v>
       </c>
       <c r="J46" t="n">
-        <v>49</v>
+        <v>525</v>
       </c>
       <c r="K46" t="n">
-        <v>49</v>
+        <v>525</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="O46" t="n">
-        <v>38</v>
+        <v>1359</v>
       </c>
       <c r="P46" t="n">
-        <v>38</v>
+        <v>444</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>444</v>
+      </c>
+      <c r="R46" t="n">
+        <v>444</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Gain On Involuntary Conversion</t>
+          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="C47" t="n">
-        <v>-80</v>
+        <v>202</v>
       </c>
       <c r="D47" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -7431,35 +7925,38 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Short-term Debt</t>
+          <t>Interest Costs Capitalized</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="C48" t="n">
-        <v>987</v>
+        <v>-42</v>
       </c>
       <c r="D48" t="n">
-        <v>987</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1802</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -7471,10 +7968,10 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7486,23 +7983,26 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1300</v>
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Redeemable Noncontrolling Interest Principal Payment</t>
+          <t>Interest Paid, Including Capitalized Interest, Operating and Investing Activities</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="C49" t="n">
-        <v>-41</v>
+        <v>160</v>
       </c>
       <c r="D49" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -7541,6 +8041,9 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7563,17 +8066,17 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-122</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>-122</v>
       </c>
       <c r="H50" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I50" t="n">
         <v>122</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
@@ -7596,6 +8099,9 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7618,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>5</v>
@@ -7627,30 +8133,33 @@
         <v>5</v>
       </c>
       <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
         <v>128</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>79</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>65</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>29</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>115</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>81</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>-31</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>-37</v>
       </c>
     </row>
@@ -7673,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>-10</v>
@@ -7682,7 +8191,7 @@
         <v>-10</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7706,6 +8215,9 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7746,13 +8258,13 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>544</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>544</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7761,6 +8273,9 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
         <v>0</v>
       </c>
     </row>
